--- a/49895_Intercuenca_Alto_Maranon_III/_raw_reportes_xlsx/IDConfig_65364_completo.xlsx
+++ b/49895_Intercuenca_Alto_Maranon_III/_raw_reportes_xlsx/IDConfig_65364_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R8d0c49d0ba224b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb9c036d7f345465e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2496</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2663</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2967</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3092</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3179</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49895_Intercuenca_Alto_Maranon_III/_raw_reportes_xlsx/IDConfig_65364_completo.xlsx
+++ b/49895_Intercuenca_Alto_Maranon_III/_raw_reportes_xlsx/IDConfig_65364_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb9c036d7f345465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0232c797b0464f96"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3258</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1957</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2117</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2221</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2721</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2796</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2833</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3383</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3275</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3242</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2796</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3133</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3271</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4248</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3438</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2929</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3238</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1900</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2179</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2283</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2265</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2279</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2479</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2333</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2396</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3054</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2396</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2465</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3171</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3722</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3371</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4688</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2583</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
